--- a/07/tech_sales.xlsx
+++ b/07/tech_sales.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10331"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/angelica/Books/O'Reilly - AI with Excel/Learning-Generative-AI-Tools-for-Excel/07/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EA7A838-D383-2541-930E-D78815EF85C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3787BA9-9003-434E-9C71-11AD0EBB6A06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="500" windowWidth="27900" windowHeight="14980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,15 +61,6 @@
     <t>john.doe@example.com</t>
   </si>
   <si>
-    <t>asmith@techsolutions.io</t>
-  </si>
-  <si>
-    <t>m.brown@innovatech.net</t>
-  </si>
-  <si>
-    <t>s.connor@clients.org</t>
-  </si>
-  <si>
     <t>li.wei@</t>
   </si>
   <si>
@@ -116,6 +107,15 @@
   </si>
   <si>
     <t>Date</t>
+  </si>
+  <si>
+    <t>asmith@example.net</t>
+  </si>
+  <si>
+    <t>m.brown@example.edu</t>
+  </si>
+  <si>
+    <t>s.connor@example.it</t>
   </si>
 </sst>
 </file>
@@ -123,7 +123,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -175,17 +175,32 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="3">
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -215,20 +230,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -243,7 +244,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{05916124-AAA2-D940-920B-FFDA0679AD50}" name="Table2" displayName="Table2" ref="A1:F8" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{05916124-AAA2-D940-920B-FFDA0679AD50}" name="Table2" displayName="Table2" ref="A1:F8" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
   <autoFilter ref="A1:F8" xr:uid="{05916124-AAA2-D940-920B-FFDA0679AD50}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{1CF74EF2-8A7C-1A41-B378-F37437EDCFE2}" name="Customer Name"/>
@@ -646,7 +647,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -657,13 +658,13 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
         <v>22</v>
-      </c>
-      <c r="E2" t="s">
-        <v>25</v>
       </c>
       <c r="F2" s="2">
         <v>45748</v>
@@ -673,17 +674,17 @@
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
-        <v>13</v>
+      <c r="B3" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
         <v>23</v>
-      </c>
-      <c r="E3" t="s">
-        <v>26</v>
       </c>
       <c r="F3" s="2">
         <v>45779</v>
@@ -693,17 +694,17 @@
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
-        <v>14</v>
+      <c r="B4" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F4" s="2">
         <v>45763</v>
@@ -713,17 +714,17 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
-        <v>15</v>
+      <c r="B5" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F5" s="2">
         <v>45812</v>
@@ -734,16 +735,16 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F6" s="2">
         <v>45752</v>
@@ -754,10 +755,10 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F7" s="2">
         <v>45783</v>
@@ -768,13 +769,13 @@
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F8" s="2">
         <v>45695</v>
